--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,673 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9886,0.0011,0.0033,0.0005</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9816,0.0002,0.0011,0.0065</t>
+  </si>
+  <si>
+    <t>0.0049,0.0001,0.0018,0.9962</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9560,0.0025,0.0209,0.0004</t>
+  </si>
+  <si>
+    <t>0.0996,0.0010,0.9098,0.0004</t>
+  </si>
+  <si>
+    <t>0.5634,0.0002,0.6809,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9642,0.0004,0.0215,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0112,0.9845,0.0074,0.0003</t>
+  </si>
+  <si>
+    <t>0.3221,0.7096,0.0048,0.0006</t>
+  </si>
+  <si>
+    <t>0.0050,0.9937,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8769,0.0004,0.1238,0.0005</t>
+  </si>
+  <si>
+    <t>0.3724,0.0033,0.6186,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0121,0.0002,0.9913,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0000,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9992,0.0010</t>
+  </si>
+  <si>
+    <t>0.1256,0.8684,0.0026,0.0019</t>
+  </si>
+  <si>
+    <t>0.9766,0.0071,0.0055,0.0035</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0007</t>
+  </si>
+  <si>
+    <t>0.0261,0.5448,0.3480,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0018,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0010,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0432,0.9576,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.9965,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.2592,0.7834,0.0024</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9966,0.0023</t>
+  </si>
+  <si>
+    <t>0.0082,0.0069,0.9826,0.0005</t>
+  </si>
+  <si>
+    <t>0.0397,0.0001,0.9786,0.0001</t>
+  </si>
+  <si>
+    <t>0.0478,0.0286,0.9054,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9923,0.0589,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.0002,0.9292</t>
+  </si>
+  <si>
+    <t>0.0045,0.9826,0.0041,0.0050</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0204,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.9929,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9989,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0019,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0031,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9918,0.0049,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9841,0.0133,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0061,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9675,0.9620,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0037,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0091,0.9945,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9896,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9974,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9369,0.0016,0.0594,0.0003</t>
+  </si>
+  <si>
+    <t>0.1753,0.0010,0.8787,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.0132,0.9975,0.0018</t>
+  </si>
+  <si>
+    <t>0.0000,0.9941,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9925,0.4314,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.1182,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9979,0.3487,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.1484,0.9894</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9939,0.0002,0.0001,0.0027</t>
-  </si>
-  <si>
-    <t>0.0228,0.0001,0.0089,0.9780</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0020,0.9994</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0047,0.9992</t>
+  </si>
+  <si>
+    <t>0.0029,0.0001,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.0001,0.9922,0.9256,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9635,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.4733,0.9891,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.1083,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9869,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.0592,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0034,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0857,0.0007,0.9235,0.0008</t>
-  </si>
-  <si>
-    <t>0.0122,0.0010,0.9888,0.0003</t>
-  </si>
-  <si>
-    <t>0.2799,0.0003,0.8525,0.0001</t>
-  </si>
-  <si>
-    <t>0.0242,0.0005,0.9758,0.0010</t>
-  </si>
-  <si>
-    <t>0.9903,0.0004,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0105,0.9877,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.7863,0.2026,0.0080,0.0008</t>
-  </si>
-  <si>
-    <t>0.0047,0.9945,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6612,0.0003,0.3953,0.0006</t>
-  </si>
-  <si>
-    <t>0.1144,0.0004,0.9091,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9995,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0117,0.0001,0.9914,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0523,0.9502,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9690,0.0246,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9996,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.9954,0.0129,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0011,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2405,0.7836,0.0025,0.0016</t>
-  </si>
-  <si>
-    <t>0.0053,0.9770,0.0725,0.0006</t>
-  </si>
-  <si>
-    <t>0.0031,0.7156,0.3543,0.0134</t>
-  </si>
-  <si>
-    <t>0.0306,0.0092,0.9261,0.0031</t>
-  </si>
-  <si>
-    <t>0.0101,0.0101,0.9735,0.0006</t>
-  </si>
-  <si>
-    <t>0.9894,0.0000,0.0120,0.0000</t>
-  </si>
-  <si>
-    <t>0.0710,0.0194,0.8915,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9966,0.0160,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9835,0.0001,0.9901</t>
-  </si>
-  <si>
-    <t>0.0017,0.9930,0.0025,0.0026</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0150,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9979,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0060,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9871,0.0094,0.0021,0.0013</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0019,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0028,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9836,0.9640,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0048,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0045,0.9923,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9927,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9988,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0465,0.0012,0.9737,0.0003</t>
-  </si>
-  <si>
-    <t>0.0832,0.0012,0.9165,0.0027</t>
-  </si>
-  <si>
-    <t>0.0008,0.0019,0.9979,0.0023</t>
-  </si>
-  <si>
-    <t>0.0000,0.9889,0.9730,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9556,0.4593,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0099,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.5432,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0678,0.9884</t>
-  </si>
-  <si>
-    <t>0.0034,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0028,0.0006,0.0055,0.9947</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0023,0.9992</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9960,0.3241,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9722,0.9920,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.8311,0.9523,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.6914,0.9430,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.9516,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9921,0.6912,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9872,0.0190,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0040,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0010,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0322,0.0006,0.9781,0.0001</t>
-  </si>
-  <si>
-    <t>0.9874,0.0002,0.0041,0.0004</t>
-  </si>
-  <si>
-    <t>0.0426,0.0001,0.9782,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9982,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0407,0.9679,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0011,0.0001</t>
+    <t>0.9927,0.0094,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0010,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.9860,0.0003,0.0049,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.0001,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9991,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0085,0.9917,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9968,0.0023,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.1167,0.9012,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.7131,0.0342,0.0949,0.0009</t>
-  </si>
-  <si>
-    <t>0.9321,0.0094,0.0239,0.0004</t>
-  </si>
-  <si>
-    <t>0.0480,0.0180,0.7312,0.0146</t>
-  </si>
-  <si>
-    <t>0.0105,0.0032,0.9764,0.0018</t>
-  </si>
-  <si>
-    <t>0.0022,0.3257,0.0021,0.9707</t>
-  </si>
-  <si>
-    <t>0.0006,0.9982,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.0001,0.0061</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9941,0.8563,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9976,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9095,0.1097,0.0027,0.0015</t>
-  </si>
-  <si>
-    <t>0.3832,0.6783,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0019,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0001</t>
+    <t>0.0002,0.9992,0.0046,0.0000</t>
+  </si>
+  <si>
+    <t>0.4360,0.6640,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9060,0.0101,0.0440,0.0007</t>
+  </si>
+  <si>
+    <t>0.0960,0.0004,0.9007,0.0028</t>
+  </si>
+  <si>
+    <t>0.2273,0.0111,0.5899,0.0024</t>
+  </si>
+  <si>
+    <t>0.0386,0.0016,0.9462,0.0022</t>
+  </si>
+  <si>
+    <t>0.0100,0.4470,0.0012,0.9080</t>
+  </si>
+  <si>
+    <t>0.0005,0.9983,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9939,0.4919,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9986,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.4735,0.5535,0.0096,0.0016</t>
+  </si>
+  <si>
+    <t>0.1204,0.8860,0.0078,0.0014</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.7194,0.9906,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6469,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0063,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.0021,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9868,0.0009,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.0108,0.0000,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.8282,0.0006,0.2215,0.0003</t>
+  </si>
+  <si>
+    <t>0.0165,0.0006,0.0000,0.9954</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9891,0.0000</t>
+  </si>
+  <si>
+    <t>0.0153,0.9837,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.7046,0.3305,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8972,0.0002,0.0001,0.1068</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0206,0.9981,0.0011</t>
+  </si>
+  <si>
+    <t>0.9790,0.0000,0.0112,0.0002</t>
+  </si>
+  <si>
+    <t>0.9368,0.0504,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.9971,0.0013,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0025,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.0104,0.9812,0.0043,0.0008</t>
+  </si>
+  <si>
+    <t>0.9058,0.0220,0.0294,0.0013</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0004,0.0006</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.8400,0.9923,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.1275,0.9967,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0033,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0028,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0003,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0313,0.0005,0.9620,0.0032</t>
-  </si>
-  <si>
-    <t>0.2469,0.0000,0.9074,0.0000</t>
-  </si>
-  <si>
-    <t>0.9135,0.0005,0.0845,0.0004</t>
-  </si>
-  <si>
-    <t>0.1498,0.0025,0.0001,0.9347</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0002,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.9865,0.0000</t>
+    <t>0.9989,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9784,0.0286,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7170,0.3264,0.0077,0.0003</t>
+  </si>
+  <si>
+    <t>0.0816,0.9391,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.4125,0.0973,0.4673,0.0023</t>
+  </si>
+  <si>
+    <t>0.9961,0.0041,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8642,0.1424,0.0113,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0055,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9628,0.0213,0.0051,0.0072</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0033,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0012,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0452,0.0004,0.9684,0.0002</t>
+  </si>
+  <si>
+    <t>0.0376,0.0159,0.9312,0.0019</t>
+  </si>
+  <si>
+    <t>0.0532,0.0199,0.9013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0208,0.0040,0.9649,0.0006</t>
+  </si>
+  <si>
+    <t>0.9226,0.0009,0.0662,0.0002</t>
+  </si>
+  <si>
+    <t>0.9330,0.0276,0.0043,0.0012</t>
+  </si>
+  <si>
+    <t>0.3035,0.0005,0.7907,0.0005</t>
+  </si>
+  <si>
+    <t>0.0679,0.9582,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.9972,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9309,0.1027,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0408,0.9707,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.1068,0.9355,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.7015,0.1236,0.0223,0.0002</t>
+  </si>
+  <si>
+    <t>0.9770,0.0003,0.0164,0.0001</t>
+  </si>
+  <si>
+    <t>0.9914,0.0011,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.4204,0.0192,0.3831,0.0033</t>
+  </si>
+  <si>
+    <t>0.9853,0.0028,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.0012,0.9865,0.0057</t>
+  </si>
+  <si>
+    <t>0.0152,0.0307,0.9408,0.0017</t>
+  </si>
+  <si>
+    <t>0.0022,0.0215,0.9905,0.0002</t>
+  </si>
+  <si>
+    <t>0.0122,0.0019,0.9815,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0526,0.9890,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0046,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0033,0.9965,0.0009</t>
+  </si>
+  <si>
+    <t>0.0365,0.0091,0.9212,0.0191</t>
+  </si>
+  <si>
+    <t>0.8493,0.0012,0.0708,0.0020</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.9968,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.2220,0.9463,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.0004,0.9952,0.0002</t>
+  </si>
+  <si>
+    <t>0.0073,0.0008,0.9838,0.0028</t>
+  </si>
+  <si>
+    <t>0.9640,0.0002,0.0338,0.0001</t>
+  </si>
+  <si>
+    <t>0.1009,0.0001,0.9422,0.0003</t>
+  </si>
+  <si>
+    <t>0.9680,0.0019,0.0161,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9965,0.0030,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0856,0.9241,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.4539,0.6163,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.4163,0.0009,0.0046,0.4791</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0075,0.9988,0.0006</t>
-  </si>
-  <si>
-    <t>0.9943,0.0000,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.6309,0.3642,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.9974,0.0009,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0011,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.3730,0.2229,0.0623,0.0063</t>
-  </si>
-  <si>
-    <t>0.7182,0.0668,0.1150,0.0061</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9679,0.0441,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.7086,0.3246,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.0732,0.9558,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0233,0.0693,0.9545,0.0009</t>
-  </si>
-  <si>
-    <t>0.9944,0.0073,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0026,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0012,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9259,0.0853,0.0033,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0181,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.8913,0.0252,0.0604,0.0017</t>
-  </si>
-  <si>
-    <t>0.0025,0.0012,0.9928,0.0012</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0021,0.9987,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0048,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0024,0.9975,0.0003</t>
-  </si>
-  <si>
-    <t>0.3174,0.0001,0.8095,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.0030,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.4792,0.0015,0.5614,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.0040,0.9888,0.0003</t>
-  </si>
-  <si>
-    <t>0.0026,0.0016,0.9925,0.0007</t>
-  </si>
-  <si>
-    <t>0.9163,0.0026,0.0590,0.0002</t>
-  </si>
-  <si>
-    <t>0.9883,0.0008,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.0359,0.0002,0.9789,0.0002</t>
-  </si>
-  <si>
-    <t>0.4959,0.6658,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.9963,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.8565,0.2504,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0188,0.9860,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.9984,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1357,0.5993,0.0616,0.0008</t>
-  </si>
-  <si>
-    <t>0.4883,0.0001,0.6899,0.0001</t>
-  </si>
-  <si>
-    <t>0.9538,0.0011,0.0135,0.0030</t>
-  </si>
-  <si>
-    <t>0.9136,0.0038,0.0587,0.0018</t>
-  </si>
-  <si>
-    <t>0.6766,0.0027,0.2562,0.0012</t>
-  </si>
-  <si>
-    <t>0.0161,0.0049,0.9597,0.0053</t>
-  </si>
-  <si>
-    <t>0.0015,0.0011,0.9956,0.0005</t>
-  </si>
-  <si>
-    <t>0.0109,0.0115,0.9780,0.0004</t>
-  </si>
-  <si>
-    <t>0.0036,0.0004,0.9935,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.4135,0.9198,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9891,0.0106,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0045,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0655,0.0211,0.8214,0.0076</t>
-  </si>
-  <si>
-    <t>0.9800,0.0024,0.0056,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0160,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0001,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9948,0.0013</t>
-  </si>
-  <si>
-    <t>0.0030,0.0009,0.9932,0.0010</t>
-  </si>
-  <si>
-    <t>0.7943,0.0003,0.2577,0.0003</t>
-  </si>
-  <si>
-    <t>0.7199,0.0001,0.3946,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0700,0.0302,0.7832,0.0022</t>
-  </si>
-  <si>
-    <t>0.0002,0.0081,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0106,0.9943,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0002,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0114,0.0021,0.9735,0.0083</t>
-  </si>
-  <si>
-    <t>0.0265,0.0011,0.9778,0.0002</t>
-  </si>
-  <si>
-    <t>0.0111,0.0077,0.9638,0.0028</t>
-  </si>
-  <si>
-    <t>0.9660,0.0016,0.0025,0.0093</t>
-  </si>
-  <si>
-    <t>0.0402,0.0123,0.0002,0.9804</t>
-  </si>
-  <si>
-    <t>0.0060,0.0001,0.0002,0.9977</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0001,0.0009</t>
+    <t>0.9980,0.0023,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0164,0.9809,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0163,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.0046,0.9886,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0718,0.0035,0.8311,0.0275</t>
+  </si>
+  <si>
+    <t>0.4477,0.0017,0.5632,0.0008</t>
+  </si>
+  <si>
+    <t>0.0037,0.0047,0.9830,0.0027</t>
+  </si>
+  <si>
+    <t>0.9753,0.0002,0.0004,0.0098</t>
+  </si>
+  <si>
+    <t>0.0128,0.0222,0.0002,0.9927</t>
+  </si>
+  <si>
+    <t>0.0028,0.0001,0.0002,0.9987</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9923,0.0009,0.0003,0.0030</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1874,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1888,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1902,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1916,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1930,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1944,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1958,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1972,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1986,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2000,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2014,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2025,10 +2040,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2042,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2053,10 +2068,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2070,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2084,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2098,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2112,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2123,10 +2138,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2140,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2154,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2168,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2182,7 +2197,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2196,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2210,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2224,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2238,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2252,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2266,7 +2281,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2280,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2294,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2308,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2322,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2350,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2364,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,10 +2390,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2392,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2406,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,10 +2432,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2434,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2448,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2462,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2473,10 +2488,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2490,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2504,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2518,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2532,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2560,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2574,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2588,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2602,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2616,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2630,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2644,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2658,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2672,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2686,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2700,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2714,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2728,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2742,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2756,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2770,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2784,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2798,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2809,10 +2824,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2826,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2840,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2854,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2868,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2882,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2893,10 +2908,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2910,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2924,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>266</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2938,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2952,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2966,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2980,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,10 +3006,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3008,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3019,10 +3034,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3033,10 +3048,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3050,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3061,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3078,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3092,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3106,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3120,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3134,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>270</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3148,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3162,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3176,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3190,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3204,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3218,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3232,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3246,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3260,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>269</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3274,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3288,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3302,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3316,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3330,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3344,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3358,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3372,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3386,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3400,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3414,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3428,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3442,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3456,7 +3471,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3467,10 +3482,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,7 +3499,7 @@
         <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3498,7 +3513,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3512,7 +3527,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3526,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3540,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3554,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3565,10 +3580,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3582,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3593,10 +3608,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3610,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3624,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>273</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3638,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3652,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3666,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>269</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3680,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3694,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3708,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3722,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>380</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3736,7 +3751,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3747,10 +3762,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3764,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3778,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3792,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3820,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3834,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3848,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3862,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3876,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3890,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3904,7 +3919,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3918,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3932,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3946,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3957,10 +3972,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3974,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3988,7 +4003,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4002,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4016,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4030,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4044,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4058,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4072,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4086,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4097,10 +4112,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4114,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4128,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4142,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4156,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>274</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4170,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4184,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4198,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>274</v>
+        <v>413</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4212,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>377</v>
+        <v>274</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4226,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4240,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4268,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,7 +4297,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4293,10 +4308,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D176" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4310,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4324,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4338,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4352,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4366,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4380,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4394,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>328</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4408,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4422,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4436,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4450,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4464,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4478,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4492,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4506,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4534,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4548,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4562,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4576,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4590,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4604,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4618,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4646,7 +4661,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4660,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4685,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4702,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4713,10 +4728,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4730,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4744,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4758,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4772,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4786,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4814,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>274</v>
+        <v>455</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4828,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4842,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4856,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4870,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4884,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4898,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4912,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>458</v>
+        <v>274</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4926,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,7 +4955,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4954,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4968,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4982,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4996,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5010,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>465</v>
+        <v>317</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5024,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5038,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>328</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5052,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5066,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5080,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5091,10 +5106,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5108,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5122,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5136,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5150,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5164,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5178,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>352</v>
+        <v>477</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5192,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5206,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>474</v>
+        <v>323</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5220,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>409</v>
+        <v>456</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5234,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5248,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5262,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5276,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5290,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5304,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5318,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5332,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5360,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5374,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5388,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>390</v>
+        <v>490</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5402,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5416,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
